--- a/exports/SCENE_SHOT_TEMPLATES.xlsx
+++ b/exports/SCENE_SHOT_TEMPLATES.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -627,7 +627,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>«То же место, что у прошлой сцены» НЕ меняет шаблон — меняет сжатие: бери вариант «место уже было» (без нового ОБЩЕГО).</t>
+          <t>T5 — только ДЛИТЕЛЬНАЯ работа руками (процесс). «Передают прошение» — T1 (двое). «Раскрывает и читает жалобу» — T2 (предмет). «Указывает на дом» — T4 (объект). Один жест руками ≠ T5.</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr"/>
@@ -635,7 +635,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>X1/X2 — только стык двух ЯЧЕЕК закадра. Сцены внутри одной ячейки на том же месте — это сжатие (T1-c2, T2-c3, T5 без K0…), не X1.</t>
+          <t>Один и тот же T* три и больше раз подряд — СТОП: прогони дерево заново для каждой такой сцены. Часть из них почти всегда T1/T2/T4/T7, а не повтор.</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr"/>
@@ -643,7 +643,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>T7 — не реплика в текущем диалоге: реплика в диалоге = хвост T1 (K4–K5), не отдельная сцена.</t>
+          <t>«То же место, что у прошлой сцены» НЕ меняет шаблон — меняет сжатие: бери вариант «место уже было» (без нового ОБЩЕГО).</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr"/>
@@ -651,39 +651,35 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>T8 = один ОБЩИЙ на один новый мир/жизнь. Семь действий в одном кабинете — не T8, а T5/T4/T2/T9/T1.</t>
+          <t>X1/X2 — только стык двух ЯЧЕЕК закадра. Сцены внутри одной ячейки на том же месте — это сжатие (T1-c2, T2-c3, T5 без K0…), не X1.</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr"/>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>T7 — не реплика в текущем диалоге: реплика в диалоге = хвост T1 (K4–K5), не отдельная сцена.</t>
+        </is>
+      </c>
       <c r="B26" s="1" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Эталонная цепь «заявление_о_краже»</t>
+          <t>T8 = один ОБЩИЙ на один новый мир/жизнь. Семь действий в одном кабинете — не T8, а T5/T4/T2/T9/T1.</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>закадр</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>Михаил пришёл к отделению полиции, зашёл внутрь, рассказал дежурному о краже и написал заявление.</t>
-        </is>
-      </c>
+      <c r="A28" s="1" t="inlineStr"/>
+      <c r="B28" s="1" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>1. улица — Михаил идёт к зданию полиции → T6 (путь A→B); короткий переход → T6-c2: ОБЩИЙ улица, вышел + ОБЩИЙ отделение, подходит к крыльцу</t>
+          <t>Эталонная цепь «заявление_о_краже»</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr"/>
@@ -691,15 +687,19 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2. отделение полиции — заходит внутрь → T3 (только смена места): ОБЩИЙ холл отделения + СРЕДНИЙ входит, снимает кепку</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr"/>
+          <t>закадр</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Михаил пришёл к отделению полиции, зашёл внутрь, рассказал дежурному о краже и написал заявление.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>3. отделение полиции — общается с дежурным полицейским → T1 (двое говорят); место уже было → T1-c2: СРЕДНИЙ с плеча Михаил + СРЕДНИЙ с плеча дежурный, без нового ОБЩЕГО</t>
+          <t>1. улица — Михаил идёт к зданию полиции → T6 (путь A→B); короткий переход → T6-c2: ОБЩИЙ улица, вышел + ОБЩИЙ отделение, подходит к крыльцу</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr"/>
@@ -707,7 +707,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>4. отделение полиции — пишет заявление о краже → T5 (руки работают); место знакомо → без K0: СРЕДНИЙ пишет + ДЕТАЛЬ рука и заявление</t>
+          <t>2. отделение полиции — заходит внутрь → T3 (только смена места): ОБЩИЙ холл отделения + СРЕДНИЙ входит, снимает кепку</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr"/>
@@ -715,10 +715,26 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
+          <t>3. отделение полиции — общается с дежурным полицейским → T1 (двое говорят); место уже было → T1-c2: СРЕДНИЙ с плеча Михаил + СРЕДНИЙ с плеча дежурный, без нового ОБЩЕГО</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>4. отделение полиции — пишет заявление о краже → T5 (руки работают); место знакомо → без K0: СРЕДНИЙ пишет + ДЕТАЛЬ рука и заявление</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
           <t>Каждая сцена — следующий шаг того же действия. Место сцен 2–4 одно → один ОБЩИЙ (у T3), дальше только сжатие. Шаблоны разные, потому что РАЗНЫЕ ответы на дерево вопросов, а не ради разнообразия.</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr"/>
+      <c r="B35" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -832,7 +848,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Двое в одном месте говорят / спорят / спрашивают. Ось одна, камера не переходит стол.</t>
+          <t>Двое или больше в одном месте ВЗАИМОДЕЙСТВУЮТ: говорят, спорят, спрашивают, слушают, передают / принимают предмет, приказывают, приветствуют, ссорятся. Действие одного направлено на другого. Есть второй живой человек в сцене и действие на него — это T1, а не T5. Ось одна, камера не переходит стол.</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -878,7 +894,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Новое место + поиск / достал / прочитал. Смысл в предмете и в том, что понял.</t>
+          <t>Новое место + предмет, который раскрывают / берут / читают / изучают: жалоба, папка, карта, письмо, реестр, свод. Смысл в предмете и в том, что понял. Один жест «передал» без изучения — не T2 (это T1).</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -923,7 +939,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Смена географии. Ещё нет диалога и нет находки. Дальше цепляй T1 / T2 / T9.</t>
+          <t>ТОЛЬКО смена географии: вошёл, стоит в новой среде. Нет взаимодействия людей, нет предмета-находки, нет работы рук, нет взгляда на объект. Дальше цепляй T1 / T2 / T9.</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -965,7 +981,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Смысл не в словах, а в том, на что смотрят: улика, человек в толпе, экран, окно.</t>
+          <t>Смысл не в словах, а в том, НА ЧТО смотрят или ЧТО показывают: улика, дом, человек в толпе, экран, окно, карта. «Указывает на», «показывает», «предъявляет», «видит среди» — это T4.</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -1008,7 +1024,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Работа / быт / улика руками: пишет, моет, режет, считает, листает.</t>
+          <t>ДЛИТЕЛЬНАЯ работа руками / быт: пишет, заполняет, подписывает, листает, моет, режет, считает, стирает, убирает, записывает. Процесс, а не один жест. Двое и действие друг на друга — это T1, не T5. Смысл в том, что понял из предмета, — T2.</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -1096,7 +1112,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Короткий слом: услышал имя, увидел, приговор, звонок. Если это реплика в том же диалоге — хвост T1 (K4–K5), не отдельная сцена.</t>
+          <t>Короткий слом: услышал имя, увидел, получил, приговор, звонок. Если это реплика в том же диалоге — хвост T1 (K4–K5), не отдельная сцена.</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -1139,7 +1155,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Годы / «а потом служил» / другая жизнь. Каждое место — новая картинка, не покрытие одной сцены.</t>
+          <t>Годы / «а потом служил» / другая жизнь / ПЕРЕЧИСЛЕНИЕ мест и владений («московский дом, усадьба и сотни крепостных»). Каждое место — новая картинка, не покрытие одной сцены.</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -3735,7 +3751,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Двое говорят / слушают друг друга?</t>
+          <t>Двое и больше ВЗАИМОДЕЙСТВУЮТ: говорят, слушают, спрашивают, передают / принимают, приказывают, приветствуют, ссорятся?</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -3752,7 +3768,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Пришёл в новое место и нашёл / взял / прочитал?</t>
+          <t>Новое место + предмет, который раскрыли / взяли / прочитали / изучают (жалоба, папка, карта, письмо, реестр)?</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -3769,7 +3785,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>ТОЛЬКО смена места, без находки? (нет диалога, работы рук, взгляда, пути, удара — иначе это не T3)</t>
+          <t>ТОЛЬКО смена места: нет взаимодействия людей, нет предмета-находки, нет работы рук, нет взгляда на объект, нет пути?</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -3786,7 +3802,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Смысл в том, НА ЧТО смотрит: улика, человек в толпе, экран, окно?</t>
+          <t>Смысл в том, НА ЧТО смотрит или ЧТО показывает: улика, дом, человек в толпе, экран, окно? («указывает на», «предъявляет» — сюда)</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -3803,7 +3819,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Руки делают работу: пишет, моет, режет, считает, листает, заполняет?</t>
+          <t>ДЛИТЕЛЬНАЯ работа руками — процесс: пишет, заполняет, подписывает, листает, моет, считает, убирает? (один жест «передал/открыл» — НЕ сюда)</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -3837,7 +3853,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Короткий слом: услышал имя, увидел, приговор, звонок?</t>
+          <t>Короткий слом: услышал имя, увидел, получил, приговор, звонок?</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -3854,7 +3870,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Годы / «а потом» / другая жизнь — несколько мест?</t>
+          <t>Годы / «а потом» / другая жизнь / перечисление мест и владений?</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">

--- a/exports/SCENE_SHOT_TEMPLATES.xlsx
+++ b/exports/SCENE_SHOT_TEMPLATES.xlsx
@@ -4147,11 +4147,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58.5" customWidth="1" min="1" max="1"/>
-    <col width="26.1" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="33.3" customWidth="1" min="2" max="2"/>
+    <col width="49.5" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4165,6 +4166,11 @@
           <t>Parent</t>
         </is>
       </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Дочерний?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -4177,6 +4183,11 @@
           <t>нет</t>
         </is>
       </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>нет — самостоятельный master, генерация с нуля</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -4189,6 +4200,11 @@
           <t>первый кадр этой локации</t>
         </is>
       </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>ДА — из PNG родителя (layout-lock)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4201,6 +4217,11 @@
           <t>обычно нет (вторая нога V)</t>
         </is>
       </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>по месту: та же комната → из PNG master места, ось своя</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -4213,6 +4234,11 @@
           <t>первый кадр этой стороны</t>
         </is>
       </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>ДА — из PNG родителя</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -4225,6 +4251,11 @@
           <t>нет (третий актёр) или master</t>
         </is>
       </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>тот же стол/место → из PNG master; иначе с нуля</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -4237,6 +4268,11 @@
           <t>нет у каждого</t>
         </is>
       </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>нет — каждый мир с нуля</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -4249,6 +4285,104 @@
           <t>нет (это уже новое место)</t>
         </is>
       </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>нет — новое место, с нуля</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>X1: следующая ячейка, то же место</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>master этой локации из прошлой ячейки</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>ДА — из PNG master прошлой ячейки</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Сжатие «место уже было» (T1-c2 / T2-c3 / T5 без K0)</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>master этой локации</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>ДА — из PNG master локации</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr"/>
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ДОЧЕРНИЕ КАДРЫ — когда используются</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Дочерний кадр = у кадра есть parent_id (по таблице T/X): он генерируется из PNG родителя (тот же сетап, другая камера), а не с нуля.</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Дочерние: то же место + другая крупность/ракурс того же действия; крупный того же лица/предмета (punch-in, тот же экземпляр); путь в том же здании; X1 и сжатие «место уже было» (parent = master локации из прошлой сцены/ячейки).</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>НЕ дочерние (parent_id = null, генерация с нуля): новое место / первый кадр сетапа; прибытие в {куда} после пути (T6-K3); монтаж мест (T8 — каждый); объект взгляда вне сетапа (T4-K2 в другом месте); X2 (два мира — два master).</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>У дочернего кадра тот же состав, что у родителя: не добавляй людей, не подменяй предмет, тот же свет. Меняются только камера и действие этого кадра.</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Каждый дочерний несёт свой дословный кусок закадра сцены (или пустой — покрытие без нового текста, если клауз меньше, чем кадров).</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr"/>
+      <c r="C17" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/SCENE_SHOT_TEMPLATES.xlsx
+++ b/exports/SCENE_SHOT_TEMPLATES.xlsx
@@ -627,7 +627,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>T5 — только ДЛИТЕЛЬНАЯ работа руками (процесс). «Передают прошение» — T1 (двое). «Раскрывает и читает жалобу» — T2 (предмет). «Указывает на дом» — T4 (объект). Один жест руками ≠ T5.</t>
+          <t>T1 — только РЕЧЬ (диалог). «Передал/принёс прошение молча» — T2 (предмет). «Приказывает», «получил возврат», «отворачивается» — T7 (слом). «Указывает на дом» — T4 (объект). T5 — только ДЛИТЕЛЬНАЯ работа руками (процесс). Один жест руками ≠ T5.</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Двое или больше в одном месте ВЗАИМОДЕЙСТВУЮТ: говорят, спорят, спрашивают, слушают, передают / принимают предмет, приказывают, приветствуют, ссорятся. Действие одного направлено на другого. Есть второй живой человек в сцене и действие на него — это T1, а не T5. Ось одна, камера не переходит стол.</t>
+          <t>Двое в одном месте ГОВОРЯТ: диалог, спор, вопрос-ответ, допрос. Реплики, а не молчаливый жест. Молчаливая передача предмета — не T1 (это T2); приказ/новость без диалога — T7. Ось одна, камера не переходит стол.</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Новое место + предмет, который раскрывают / берут / читают / изучают: жалоба, папка, карта, письмо, реестр, свод. Смысл в предмете и в том, что понял. Один жест «передал» без изучения — не T2 (это T1).</t>
+          <t>Новое место + предмет, который раскрывают / берут / читают / передают / приносят / изучают: жалоба, папка, карта, письмо, реестр, свод, прошение. Смысл в предмете и в том, что понял.</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Короткий слом: услышал имя, увидел, получил, приговор, звонок. Если это реплика в том же диалоге — хвост T1 (K4–K5), не отдельная сцена.</t>
+          <t>Короткий слом: услышал имя, увидел, получил (возврат/приговор/ответ), приказ, отказ, звонок. Если это реплика в том же диалоге — хвост T1 (K4–K5), не отдельная сцена.</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Двое и больше ВЗАИМОДЕЙСТВУЮТ: говорят, слушают, спрашивают, передают / принимают, приказывают, приветствуют, ссорятся?</t>
+          <t>Двое ГОВОРЯТ друг с другом: реплики, спор, вопрос-ответ, допрос?</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Новое место + предмет, который раскрыли / взяли / прочитали / изучают (жалоба, папка, карта, письмо, реестр)?</t>
+          <t>Новое место + предмет, который раскрыли / взяли / прочитали / передали / принесли (жалоба, папка, карта, письмо, реестр, прошение)?</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Короткий слом: услышал имя, увидел, получил, приговор, звонок?</t>
+          <t>Короткий слом: услышал имя, увидел, получил возврат/ответ, приказ, отказ, приговор, звонок?</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">

--- a/exports/SCENE_SHOT_TEMPLATES.xlsx
+++ b/exports/SCENE_SHOT_TEMPLATES.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -735,6 +735,62 @@
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr"/>
+      <c r="B36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Эталонная цепь «наказание_показать_не_назвать»</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>закадр</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>За малейший проступок Салтычиха наказывала служанок, и многие не выживали.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>1. двор усадьбы — служанку тащат к столбу и привязывают руки → T3 (новое место): ОБЩИЙ двор со столбом + СРЕДНИЙ руки затягивают верёвку</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>2. двор усадьбы — Салтычиха смотрит, как хлыст поднимается над спиной служанки → T4 (взгляд на объект): СРЕДНИЙ Салтычиха смотрит + ОБЩИЙ хлыст над спиной + КРУПНЫЙ её лицо без эмоций</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>3. двор усадьбы — после: простыня накрывает тело, свеча гаснет → T10 (уход/точка): КРУПНЫЙ рука накрывает простыню + ОБЩИЙ двор пустеет</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>«Наказывала» — показано САМО наказание; «не выживали» — показана смерть (простыня, свеча). Эмоция — через поступок (смотрит без эмоций), не подпись. Кадры каждой сцены — шаги одного действия, не ракурсы одной позы.</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
